--- a/AAII_Financials/Yearly/APA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/APA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
   <si>
     <t>APA</t>
   </si>
@@ -1134,10 +1134,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6021000</v>
+        <v>6014000</v>
       </c>
       <c r="E17" s="3">
-        <v>7407000</v>
+        <v>7403000</v>
       </c>
       <c r="F17" s="3">
         <v>4668000</v>
@@ -1185,10 +1185,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>2664000</v>
+        <v>2671000</v>
       </c>
       <c r="E18" s="3">
-        <v>2056000</v>
+        <v>2060000</v>
       </c>
       <c r="F18" s="3">
         <v>3425000</v>
@@ -1256,11 +1256,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>7000</v>
       </c>
       <c r="E20" s="3">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
@@ -1868,11 +1868,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-7000</v>
       </c>
       <c r="E32" s="3">
-        <v>-2000</v>
+        <v>-6000</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
